--- a/src/test/resources/testdata/SettingsData.xlsx
+++ b/src/test/resources/testdata/SettingsData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Local\DXC\iot-fe-automation\src\test\resources\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Downloads\QA_Automation\s2-selenium\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA4B24E-E2C7-469C-8D9B-82A0748EE05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E48C72-04EC-480E-922A-82CDB443E42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -136,9 +136,6 @@
     <t>Save with no values entered (empty save)</t>
   </si>
   <si>
-    <t>thresholds saved.</t>
-  </si>
-  <si>
     <t>TC-FE-A052</t>
   </si>
   <si>
@@ -158,6 +155,9 @@
   </si>
   <si>
     <t>Save only upper threshold</t>
+  </si>
+  <si>
+    <t>saved successfully</t>
   </si>
 </sst>
 </file>
@@ -574,10 +574,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="35.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="6" width="17" customWidth="1"/>
@@ -585,7 +585,7 @@
     <col min="8" max="8" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -611,7 +611,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>36</v>
       </c>
@@ -625,10 +625,10 @@
         <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -643,7 +643,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>12</v>
@@ -652,7 +652,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -678,7 +678,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -702,7 +702,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -726,7 +726,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -750,7 +750,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
@@ -774,7 +774,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>30</v>
       </c>
@@ -800,7 +800,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
         <v>33</v>
       </c>
@@ -826,12 +826,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>10</v>
@@ -846,18 +846,18 @@
         <v>50</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>10</v>
@@ -874,12 +874,12 @@
       </c>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>10</v>
